--- a/artfynd/A 24959-2022 artfynd.xlsx
+++ b/artfynd/A 24959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,132 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122060520</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90726</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570057</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6479062</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24959-2022 artfynd.xlsx
+++ b/artfynd/A 24959-2022 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>122060520</v>
       </c>
       <c r="B3" t="n">
-        <v>90763</v>
+        <v>90773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 24959-2022 artfynd.xlsx
+++ b/artfynd/A 24959-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122030002</v>
       </c>
       <c r="B2" t="n">
-        <v>9395</v>
+        <v>9400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>122060520</v>
       </c>
       <c r="B3" t="n">
-        <v>90773</v>
+        <v>90785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 24959-2022 artfynd.xlsx
+++ b/artfynd/A 24959-2022 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>122060520</v>
       </c>
       <c r="B3" t="n">
-        <v>90785</v>
+        <v>90792</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 24959-2022 artfynd.xlsx
+++ b/artfynd/A 24959-2022 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>122060520</v>
       </c>
       <c r="B3" t="n">
-        <v>90792</v>
+        <v>90797</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,11 +820,6 @@
       </c>
       <c r="E3" t="n">
         <v>4660</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Rävticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -893,11 +888,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
